--- a/ig/DM-FEVRIER-2026/CodeSystem-tre-r402-activite-enseignement-regulee.xlsx
+++ b/ig/DM-FEVRIER-2026/CodeSystem-tre-r402-activite-enseignement-regulee.xlsx
@@ -43,7 +43,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>TreR401ActiviteEnseignementRegulee</t>
+    <t>TreR402ActiviteEnseignementRegulee</t>
   </si>
   <si>
     <t>Title</t>
